--- a/data/trans_orig/P36B17-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B17-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>74892</t>
+          <t>84071</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51852</t>
+          <t>61013</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>104269</t>
+          <t>112816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44348</t>
+          <t>50071</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>35481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61595</t>
+          <t>70269</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>119240</t>
+          <t>134142</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92597</t>
+          <t>104232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152698</t>
+          <t>166515</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95985</t>
+          <t>93909</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67300</t>
+          <t>70188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128558</t>
+          <t>125413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>105585</t>
+          <t>120095</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84652</t>
+          <t>99041</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129489</t>
+          <t>144106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>201570</t>
+          <t>214005</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168069</t>
+          <t>179970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243630</t>
+          <t>253692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>161858</t>
+          <t>159534</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131094</t>
+          <t>124574</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>195214</t>
+          <t>188589</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>122326</t>
+          <t>141515</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>99448</t>
+          <t>113823</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146361</t>
+          <t>165946</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>284184</t>
+          <t>301050</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>246742</t>
+          <t>259935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>328550</t>
+          <t>341604</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52469</t>
+          <t>51114</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32036</t>
+          <t>32875</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83545</t>
+          <t>78116</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31355</t>
+          <t>37829</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>24663</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46109</t>
+          <t>56841</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>83824</t>
+          <t>88944</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57834</t>
+          <t>65863</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116678</t>
+          <t>118934</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>19164</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27860</t>
+          <t>35453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8599</t>
+          <t>12058</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18903</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>31222</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40694</t>
+          <t>53152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>312213</t>
+          <t>361569</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>312213</t>
+          <t>361569</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>312213</t>
+          <t>361569</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>712200</t>
+          <t>769362</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>712200</t>
+          <t>769362</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>712200</t>
+          <t>769362</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60961</t>
+          <t>69628</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44940</t>
+          <t>51073</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81130</t>
+          <t>91270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>74316</t>
+          <t>89729</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47316</t>
+          <t>72369</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95865</t>
+          <t>107568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>135278</t>
+          <t>159357</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101995</t>
+          <t>135319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163897</t>
+          <t>187960</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>116440</t>
+          <t>137090</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95115</t>
+          <t>113973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140884</t>
+          <t>162960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>173090</t>
+          <t>192408</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103988</t>
+          <t>167567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>208559</t>
+          <t>213672</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>289530</t>
+          <t>329498</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>221947</t>
+          <t>295134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328393</t>
+          <t>365752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>184175</t>
+          <t>201911</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>157922</t>
+          <t>173467</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>213732</t>
+          <t>229339</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>232193</t>
+          <t>179297</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179727</t>
+          <t>159134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>339428</t>
+          <t>203738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>416368</t>
+          <t>381208</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>363578</t>
+          <t>349790</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>542347</t>
+          <t>419998</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -1746,69 +1746,69 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49877</t>
+          <t>54934</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35969</t>
+          <t>39803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67723</t>
+          <t>72899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>30209</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20284</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>42556</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>8,53%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>26120</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14333</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>39603</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>63</t>
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>75997</t>
+          <t>85143</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55158</t>
+          <t>66105</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98452</t>
+          <t>108346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22217</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>16084</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8003</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>32165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>421917</t>
+          <t>475304</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>421917</t>
+          <t>475304</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>421917</t>
+          <t>475304</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>511341</t>
+          <t>499134</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>511341</t>
+          <t>499134</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>511341</t>
+          <t>499134</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>933258</t>
+          <t>974439</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>933258</t>
+          <t>974439</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>933258</t>
+          <t>974439</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>99252</t>
+          <t>120913</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82531</t>
+          <t>100015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118817</t>
+          <t>144002</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>104073</t>
+          <t>128126</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90291</t>
+          <t>110438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119986</t>
+          <t>145930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>203325</t>
+          <t>249039</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180328</t>
+          <t>223867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>227759</t>
+          <t>277132</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -2202,67 +2202,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>204854</t>
+          <t>231801</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>182680</t>
+          <t>208085</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>229444</t>
+          <t>256674</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>37,34%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,52%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,34%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>236921</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>217773</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>258817</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>38,2%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,06%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>42,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>209164</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>191387</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>227313</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,68%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>414018</t>
+          <t>468722</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>381389</t>
+          <t>438849</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>444978</t>
+          <t>503734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,59%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>183481</t>
+          <t>212247</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>158775</t>
+          <t>186864</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>206306</t>
+          <t>237752</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>183411</t>
+          <t>207430</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>165358</t>
+          <t>187721</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>201964</t>
+          <t>226061</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>366892</t>
+          <t>419677</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>338965</t>
+          <t>388404</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>393732</t>
+          <t>450965</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36499</t>
+          <t>42586</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26362</t>
+          <t>30917</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50009</t>
+          <t>58363</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>35771</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27186</t>
+          <t>29197</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45435</t>
+          <t>51169</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>72270</t>
+          <t>81454</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58936</t>
+          <t>65578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87365</t>
+          <t>99759</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>22711</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>20559</t>
+          <t>22214</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>13910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32575</t>
+          <t>32861</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>540727</t>
+          <t>620269</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>540727</t>
+          <t>620269</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>540727</t>
+          <t>620269</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1077065</t>
+          <t>1241106</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1077065</t>
+          <t>1241106</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1077065</t>
+          <t>1241106</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>143482</t>
+          <t>157865</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62934</t>
+          <t>137176</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>208762</t>
+          <t>179361</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>164157</t>
+          <t>179659</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138821</t>
+          <t>161208</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>185918</t>
+          <t>198947</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>307639</t>
+          <t>337524</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>193814</t>
+          <t>309903</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>377186</t>
+          <t>367173</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>210862</t>
+          <t>236271</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95868</t>
+          <t>213491</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>302877</t>
+          <t>263152</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>257289</t>
+          <t>282144</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>263510</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>281534</t>
+          <t>306933</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>468151</t>
+          <t>518415</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>307151</t>
+          <t>487659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>571309</t>
+          <t>552529</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>232704</t>
+          <t>244116</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91805</t>
+          <t>217639</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>335023</t>
+          <t>272620</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>251505</t>
+          <t>233004</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>222211</t>
+          <t>212578</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>335287</t>
+          <t>252545</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>484210</t>
+          <t>477121</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>313095</t>
+          <t>445467</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>595969</t>
+          <t>508900</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -3110,69 +3110,69 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>33003</t>
+          <t>35144</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52765</t>
+          <t>49267</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>32868</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>24839</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>43679</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>5,94%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>31117</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>22174</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>40045</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>80</t>
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>64120</t>
+          <t>68013</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38305</t>
+          <t>53875</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85184</t>
+          <t>84393</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>267736</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26799</t>
+          <t>17927</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>627687</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>275484</t>
+          <t>35357</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31928</t>
+          <t>24792</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>707839</t>
+          <t>49501</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>711816</t>
+          <t>735812</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>711816</t>
+          <t>735812</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>711816</t>
+          <t>735812</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1599603</t>
+          <t>1436429</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1599603</t>
+          <t>1436429</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1599603</t>
+          <t>1436429</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>158106</t>
+          <t>172826</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>139063</t>
+          <t>151852</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>179751</t>
+          <t>193134</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>180745</t>
+          <t>204144</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>165302</t>
+          <t>185338</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>198921</t>
+          <t>222306</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>338850</t>
+          <t>376970</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>311164</t>
+          <t>348187</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>365343</t>
+          <t>405739</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>192148</t>
+          <t>211520</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>170573</t>
+          <t>188571</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>213291</t>
+          <t>233517</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>205862</t>
+          <t>227123</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>186883</t>
+          <t>209862</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>221105</t>
+          <t>245879</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>398010</t>
+          <t>438643</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>372451</t>
+          <t>408968</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>425442</t>
+          <t>466628</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>173745</t>
+          <t>183508</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>153316</t>
+          <t>161396</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>195158</t>
+          <t>207806</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>134545</t>
+          <t>148385</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>119984</t>
+          <t>132002</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>150785</t>
+          <t>165314</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>308290</t>
+          <t>331893</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>282206</t>
+          <t>306392</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>333924</t>
+          <t>360759</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>28239</t>
+          <t>31368</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41191</t>
+          <t>42781</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>19085</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>13161</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24270</t>
+          <t>26549</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>45601</t>
+          <t>50452</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>38946</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>58852</t>
+          <t>64313</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>15987</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>24560</t>
+          <t>28732</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>560399</t>
+          <t>608501</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>560399</t>
+          <t>608501</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>560399</t>
+          <t>608501</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>546339</t>
+          <t>607312</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>546339</t>
+          <t>607312</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>546339</t>
+          <t>607312</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1106738</t>
+          <t>1215813</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1106738</t>
+          <t>1215813</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1106738</t>
+          <t>1215813</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>142592</t>
+          <t>156697</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>126520</t>
+          <t>140307</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>156827</t>
+          <t>172239</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>373968</t>
+          <t>186307</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>248513</t>
+          <t>171318</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>530521</t>
+          <t>201011</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>516559</t>
+          <t>343004</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>385486</t>
+          <t>320660</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>738936</t>
+          <t>366169</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>117466</t>
+          <t>130330</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>104187</t>
+          <t>116406</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>133673</t>
+          <t>146549</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>134000</t>
+          <t>145402</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>41904</t>
+          <t>131784</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>209623</t>
+          <t>160106</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>251465</t>
+          <t>275732</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>124766</t>
+          <t>256183</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>326747</t>
+          <t>296744</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>81675</t>
+          <t>90922</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>70250</t>
+          <t>77867</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>96479</t>
+          <t>105206</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>85295</t>
+          <t>93617</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>27418</t>
+          <t>82193</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>134642</t>
+          <t>107230</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>166970</t>
+          <t>184538</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>86203</t>
+          <t>166833</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>220843</t>
+          <t>205820</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>20697</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>14265</t>
+          <t>15969</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>29599</t>
+          <t>33548</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>29001</t>
+          <t>32078</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>13700</t>
+          <t>22799</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>42676</t>
+          <t>42581</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>12492</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>366812</t>
+          <t>405674</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>366812</t>
+          <t>405674</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>366812</t>
+          <t>405674</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>603668</t>
+          <t>436640</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>603668</t>
+          <t>436640</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>603668</t>
+          <t>436640</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>970479</t>
+          <t>842313</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>970479</t>
+          <t>842313</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>970479</t>
+          <t>842313</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>141225</t>
+          <t>154090</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>127995</t>
+          <t>139008</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>155754</t>
+          <t>169261</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>239185</t>
+          <t>261912</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>225361</t>
+          <t>245244</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>253664</t>
+          <t>277612</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,17 +4887,17 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>380410</t>
+          <t>416001</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>360946</t>
+          <t>391527</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>398393</t>
+          <t>436870</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,5%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>79879</t>
+          <t>88233</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>67499</t>
+          <t>74652</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>92189</t>
+          <t>100535</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>117116</t>
+          <t>126568</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>104644</t>
+          <t>112850</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>128987</t>
+          <t>141605</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,22 +5000,22 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>196995</t>
+          <t>214801</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>181284</t>
+          <t>198227</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>216287</t>
+          <t>236857</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>51685</t>
+          <t>56152</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>41520</t>
+          <t>45753</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>63046</t>
+          <t>67943</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>53682</t>
+          <t>59160</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>44355</t>
+          <t>49243</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>63846</t>
+          <t>71684</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>105367</t>
+          <t>115312</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>90826</t>
+          <t>100410</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>119434</t>
+          <t>133279</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>21037</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>14703</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>25434</t>
+          <t>29770</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,22 +5304,22 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>282192</t>
+          <t>309665</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>282192</t>
+          <t>309665</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>282192</t>
+          <t>309665</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>424909</t>
+          <t>463600</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>424909</t>
+          <t>463600</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>424909</t>
+          <t>463600</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>707101</t>
+          <t>773265</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>707101</t>
+          <t>773265</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>707101</t>
+          <t>773265</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>820511</t>
+          <t>916089</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>617626</t>
+          <t>860785</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>901733</t>
+          <t>971510</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1180791</t>
+          <t>1099948</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1009632</t>
+          <t>1050639</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1640024</t>
+          <t>1150676</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>2001302</t>
+          <t>2016037</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1799354</t>
+          <t>1948160</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2427695</t>
+          <t>2091280</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1017634</t>
+          <t>1129153</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>758741</t>
+          <t>1068265</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1118444</t>
+          <t>1184929</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1202105</t>
+          <t>1330663</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>962632</t>
+          <t>1283771</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1303542</t>
+          <t>1384538</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2219740</t>
+          <t>2459816</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1935533</t>
+          <t>2385739</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2373973</t>
+          <t>2546057</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1069325</t>
+          <t>1148391</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>810350</t>
+          <t>1091079</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1167781</t>
+          <t>1215568</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1062957</t>
+          <t>1062408</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>889481</t>
+          <t>1005997</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1215676</t>
+          <t>1111050</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2132282</t>
+          <t>2210799</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1876472</t>
+          <t>2122245</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2314624</t>
+          <t>2299833</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>227669</t>
+          <t>246721</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>182622</t>
+          <t>209791</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>271996</t>
+          <t>285239</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>161779</t>
+          <t>180400</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>127510</t>
+          <t>158063</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>187599</t>
+          <t>210318</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>389448</t>
+          <t>427120</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>326619</t>
+          <t>379351</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>440276</t>
+          <t>472869</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>320293</t>
+          <t>88037</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>75209</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1087171</t>
+          <t>111532</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>43380</t>
+          <t>50918</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>30744</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>57956</t>
+          <t>66691</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>363673</t>
+          <t>138954</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>114201</t>
+          <t>116279</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1198403</t>
+          <t>167985</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3455432</t>
+          <t>3528391</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3455432</t>
+          <t>3528391</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3455432</t>
+          <t>3528391</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3651012</t>
+          <t>3724336</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3651012</t>
+          <t>3724336</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3651012</t>
+          <t>3724336</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>7106444</t>
+          <t>7252727</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7106444</t>
+          <t>7252727</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>7106444</t>
+          <t>7252727</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
